--- a/test/实验数据.xlsx
+++ b/test/实验数据.xlsx
@@ -8,24 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mylife_yanjiu\project\rag_sva\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203940CC-EB87-43F8-8B9A-C9A8A1FD404E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E70923-396E-41B3-8347-6E03F5F17E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="148">
   <si>
     <t>设计</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,6 +66,1160 @@
   </si>
   <si>
     <t>答案正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Design Source Code</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Example Assertion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comment String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temperature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>% Correct Simulated Assertions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuggyDUT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoCom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailedEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DetailedCom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG-on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>design0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden/17E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>design1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden/4E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>design2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>design3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden/59E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>design4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>design5</t>
+  </si>
+  <si>
+    <t>design6</t>
+  </si>
+  <si>
+    <t>design7</t>
+  </si>
+  <si>
+    <t>design8</t>
+  </si>
+  <si>
+    <t>design9</t>
+  </si>
+  <si>
+    <t>✓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden/16128E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8064E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden/28E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>28E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>✕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>24E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>60E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>20E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden/36861E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>48381E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden/960E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>960E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>960E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden/340E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>340E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>59E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>golden/16E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>49E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>12E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>16E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>17E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>16E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8064E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="3"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-stage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>93E(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-stage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>naive-RAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>optimized-RAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>average</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rag_ref</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG效果评估/item=10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG效果评估/item=20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高忠实度，扩充条目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>generate assertion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compiled assertion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Correct Assertions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>% Correct Assertions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enhanced-RAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定性对比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g2: OpenAssert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示工程？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>威胁模型生成？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试平台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g6:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenTitan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非安全知识库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HackDAC21 OpenTitan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g11: LASP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSA,DES,SHA512,AES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g19: LASSO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CEP,OpenTitan,HackDAC24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安全知识库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neorv32 SoC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g15: ThreatLens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g8: AssertLLM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SVA生成？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG效果评估/item=90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>design2</t>
+  </si>
+  <si>
+    <t>design3</t>
+  </si>
+  <si>
+    <t>design10</t>
+  </si>
+  <si>
+    <r>
+      <t>3/3/2/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>6/6/3/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5/5/0/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5/5/2/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3/3/1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2/2/1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2/2/2/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5/5/1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>39/17=0.4359</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>6/6/4/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1/1/1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4/0/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1/1/0/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4/4/2/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✓</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17/12=0.7059</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2/0/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✕</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20/9=0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1阶简单RAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三阶简单RAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三阶优化RAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Method</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识库类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g21：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -59,7 +1227,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +1243,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -103,10 +1299,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +1338,57 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -397,255 +1671,252 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="18.77734375" defaultRowHeight="28.05" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="18.77734375" style="2"/>
+    <col min="1" max="16384" width="18.77734375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+    </row>
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
         <v>0</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="10">
         <v>0.3125</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="10">
         <v>0.77400000000000002</v>
       </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
         <v>0.59589999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2">
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="10">
         <v>0.7863</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="1">
         <v>0.86670000000000003</v>
       </c>
-      <c r="E4" s="2">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10">
         <v>0.40150000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
         <v>2</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="10">
         <v>0.2273</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="10">
         <v>0.83230000000000004</v>
       </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10">
         <v>0.58850000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="10">
         <v>0.625</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="10">
         <v>0.79710000000000003</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="1">
         <v>0.5</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="10">
         <v>0</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="10">
         <v>0.50470000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
         <v>4</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="10">
         <v>0.30559999999999998</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="10">
         <v>0.78910000000000002</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="1">
         <v>0.95</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="10">
         <v>0.83330000000000004</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="10">
         <v>0.75729999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+    <row r="8" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
         <v>5</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="10">
         <v>0</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="10">
         <v>0.78080000000000005</v>
       </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="10">
         <v>0.875</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="10">
         <v>0.40389999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+    <row r="9" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
         <v>6</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="10">
         <v>0.13789999999999999</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="10">
         <v>0.79020000000000001</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="1">
         <v>0.67920000000000003</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="10">
         <v>0</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="10">
         <v>0.62270000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+    <row r="10" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
         <v>7</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="10">
         <v>9.5200000000000007E-2</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="10">
         <v>0.7681</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="F10" s="2">
+      <c r="D10" s="1"/>
+      <c r="F10" s="10">
         <v>0.622</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+    <row r="11" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
         <v>8</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="10">
         <v>4.3499999999999997E-2</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="10">
         <v>0.79330000000000001</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="F11" s="2">
+      <c r="D11" s="1"/>
+      <c r="F11" s="10">
         <v>0.48809999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+    <row r="12" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
         <v>9</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="10">
         <v>0.17299999999999999</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="10">
         <v>0.77700000000000002</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="F12" s="2">
+      <c r="D12" s="1"/>
+      <c r="F12" s="10">
         <v>0.68079999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="4"/>
+    <row r="13" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="1"/>
     </row>
     <row r="17" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="4"/>
+      <c r="D17" s="1"/>
     </row>
     <row r="18" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="4"/>
+      <c r="D18" s="1"/>
     </row>
     <row r="19" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="4"/>
+      <c r="D19" s="1"/>
     </row>
     <row r="20" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="4"/>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="4"/>
+      <c r="D21" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -654,4 +1925,4294 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF19DE99-23A4-44BD-B675-0AE246CEEB40}">
+  <dimension ref="A1:N64"/>
+  <sheetFormatPr defaultColWidth="18.77734375" defaultRowHeight="28.05" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="18.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="K1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="K2" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="4" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.89</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="8"/>
+      <c r="K4" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0.93</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="8"/>
+      <c r="K5" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="K7" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N16" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N39" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N49" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>4</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="F55" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="I55" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="J55" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="K55" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="L55" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>5</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G56" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="H56" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="I56" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K56" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>6</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H57" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="I57" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J57" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="K57" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>4</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F59" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="G59" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="H59" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="I59" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J59" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="K59" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="L59" s="26">
+        <v>0.44290000000000002</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>5</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="I60" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="J60" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="K60" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="L60" s="25">
+        <v>0.61429999999999996</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="N60" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="8">
+        <v>6</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="I61" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="J61" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="K61" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="L61" s="25">
+        <v>0.77139999999999997</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>2</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="G63" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H63" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="I63" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J63" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="K63" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="L63" s="25">
+        <v>0.87139999999999995</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>3</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="G64" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="H64" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="I64" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="J64" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="K64" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="L64" s="25">
+        <v>0.92859999999999998</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF40AC2-0D96-4FFD-832B-31582FF7F1B0}">
+  <dimension ref="A1:R61"/>
+  <sheetFormatPr defaultColWidth="16.77734375" defaultRowHeight="28.05" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="16.77734375" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="28"/>
+      <c r="F2" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="29"/>
+      <c r="H2" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="28"/>
+    </row>
+    <row r="3" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="28"/>
+      <c r="B3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="N3" s="9"/>
+    </row>
+    <row r="4" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>0</v>
+      </c>
+      <c r="B4" s="10">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0.44440000000000002</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0.75019999999999998</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0.80879999999999996</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="G4" s="10">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="J4" s="10">
+        <v>0.69340000000000002</v>
+      </c>
+      <c r="K4" s="11">
+        <v>0.80430000000000001</v>
+      </c>
+      <c r="N4" s="9"/>
+    </row>
+    <row r="5" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10">
+        <v>0.15379999999999999</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0.58819999999999995</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.73770000000000002</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.74380000000000002</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0.69579999999999997</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0.58040000000000003</v>
+      </c>
+      <c r="N5" s="9"/>
+    </row>
+    <row r="6" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10">
+        <v>0.52380000000000004</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0.7903</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10">
+        <v>0.64410000000000001</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0.84870000000000001</v>
+      </c>
+      <c r="N6" s="9"/>
+    </row>
+    <row r="7" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>3</v>
+      </c>
+      <c r="B7" s="10">
+        <v>0.36359999999999998</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0.74809999999999999</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0.75049999999999994</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0.76219999999999999</v>
+      </c>
+      <c r="K7" s="11">
+        <v>0.51459999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10">
+        <v>0.30769999999999997</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.4375</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0.76019999999999999</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0.74070000000000003</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0.7379</v>
+      </c>
+      <c r="K8" s="11">
+        <v>0.80349999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>5</v>
+      </c>
+      <c r="B9" s="10">
+        <v>0.26669999999999999</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0.63639999999999997</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0.75739999999999996</v>
+      </c>
+      <c r="E9" s="10">
+        <v>0.80149999999999999</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="J9" s="10">
+        <v>0.79910000000000003</v>
+      </c>
+      <c r="K9" s="11">
+        <v>0.71109999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10">
+        <v>0.60570000000000002</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.6875</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.73729999999999996</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0.79330000000000001</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="10">
+        <v>0.78169999999999995</v>
+      </c>
+      <c r="K10" s="11">
+        <v>0.75990000000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>7</v>
+      </c>
+      <c r="B11" s="10">
+        <v>0.3125</v>
+      </c>
+      <c r="C11" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.74990000000000001</v>
+      </c>
+      <c r="E11" s="10">
+        <v>0.76910000000000001</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J11" s="10">
+        <v>0.66069999999999995</v>
+      </c>
+      <c r="K11" s="11">
+        <v>0.61609999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0.23530000000000001</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0.76290000000000002</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0.77059999999999995</v>
+      </c>
+      <c r="F12" s="10">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0.51690000000000003</v>
+      </c>
+      <c r="K12" s="11">
+        <v>0.4551</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0.26910000000000001</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.72870000000000001</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.75980000000000003</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="8">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0.87539999999999996</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0.88839999999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="8">
+        <f>AVERAGE(B4:B13)</f>
+        <v>0.32028999999999996</v>
+      </c>
+      <c r="C14" s="8">
+        <f t="shared" ref="C14:K14" si="0">AVERAGE(C4:C13)</f>
+        <v>0.51863999999999999</v>
+      </c>
+      <c r="D14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.75226999999999999</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.77714000000000005</v>
+      </c>
+      <c r="F14" s="8">
+        <f>AVERAGE(F4:F13)</f>
+        <v>0.8333299999999999</v>
+      </c>
+      <c r="G14" s="8">
+        <f>AVERAGE(G4:G13)</f>
+        <v>0.88333000000000017</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.83416999999999997</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.71672000000000002</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.69821</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+    </row>
+    <row r="16" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+    </row>
+    <row r="17" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="29"/>
+      <c r="H17" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K17" s="28"/>
+      <c r="M17" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="28"/>
+      <c r="B18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+    </row>
+    <row r="19" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12">
+        <v>0</v>
+      </c>
+      <c r="B19" s="12">
+        <v>0</v>
+      </c>
+      <c r="C19" s="12">
+        <v>0.46150000000000002</v>
+      </c>
+      <c r="D19" s="12">
+        <v>0.75770000000000004</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0.80879999999999996</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="G19" s="12">
+        <v>1</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="I19" s="13">
+        <v>1</v>
+      </c>
+      <c r="J19" s="12">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0.72109999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <v>1</v>
+      </c>
+      <c r="B20" s="12">
+        <v>0.15379999999999999</v>
+      </c>
+      <c r="C20" s="12">
+        <v>0.35709999999999997</v>
+      </c>
+      <c r="D20" s="12">
+        <v>0.74380000000000002</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="F20" s="12">
+        <v>1</v>
+      </c>
+      <c r="G20" s="12">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1</v>
+      </c>
+      <c r="I20" s="13">
+        <v>0.628</v>
+      </c>
+      <c r="J20" s="12">
+        <v>0.71130000000000004</v>
+      </c>
+      <c r="K20" s="12">
+        <v>0.77939999999999998</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="R20" s="6"/>
+    </row>
+    <row r="21" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <v>2</v>
+      </c>
+      <c r="B21" s="12">
+        <v>0.44829999999999998</v>
+      </c>
+      <c r="C21" s="12">
+        <v>0.45729999999999998</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0.79179999999999995</v>
+      </c>
+      <c r="E21" s="12">
+        <v>0.8085</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="I21" s="13">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="J21" s="12">
+        <v>0.49880000000000002</v>
+      </c>
+      <c r="K21" s="12">
+        <v>0.81469999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12">
+        <v>3</v>
+      </c>
+      <c r="B22" s="12">
+        <v>0.2727</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0.86609999999999998</v>
+      </c>
+      <c r="D22" s="12">
+        <v>0.74819999999999998</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0.76559999999999995</v>
+      </c>
+      <c r="F22" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="12">
+        <v>1</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="I22" s="13">
+        <v>0.75</v>
+      </c>
+      <c r="J22" s="12">
+        <v>0.72050000000000003</v>
+      </c>
+      <c r="K22" s="12">
+        <v>0.79649999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <v>4</v>
+      </c>
+      <c r="B23" s="12">
+        <v>0.30769999999999997</v>
+      </c>
+      <c r="C23" s="12">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="D23" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="E23" s="12">
+        <v>0.81669999999999998</v>
+      </c>
+      <c r="F23" s="12">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="H23" s="8">
+        <v>1</v>
+      </c>
+      <c r="I23" s="13">
+        <v>1</v>
+      </c>
+      <c r="J23" s="12">
+        <v>0.69940000000000002</v>
+      </c>
+      <c r="K23" s="12">
+        <v>0.79500000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12">
+        <v>5</v>
+      </c>
+      <c r="B24" s="12">
+        <v>0.1429</v>
+      </c>
+      <c r="C24" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="D24" s="12">
+        <v>0.75660000000000005</v>
+      </c>
+      <c r="E24" s="12">
+        <v>0.80149999999999999</v>
+      </c>
+      <c r="F24" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I24" s="13">
+        <v>1</v>
+      </c>
+      <c r="J24" s="12">
+        <v>0.74239999999999995</v>
+      </c>
+      <c r="K24" s="12">
+        <v>0.48899999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <v>6</v>
+      </c>
+      <c r="B25" s="12">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="C25" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="D25" s="12">
+        <v>0.73680000000000001</v>
+      </c>
+      <c r="E25" s="12">
+        <v>0.79330000000000001</v>
+      </c>
+      <c r="F25" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G25" s="12">
+        <v>1</v>
+      </c>
+      <c r="H25" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="I25" s="13">
+        <v>1</v>
+      </c>
+      <c r="J25" s="12">
+        <v>0.54330000000000001</v>
+      </c>
+      <c r="K25" s="12">
+        <v>0.7238</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12">
+        <v>7</v>
+      </c>
+      <c r="B26" s="12">
+        <v>0.1875</v>
+      </c>
+      <c r="C26" s="12">
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="D26" s="12">
+        <v>0.75509999999999999</v>
+      </c>
+      <c r="E26" s="12">
+        <v>0.80510000000000004</v>
+      </c>
+      <c r="F26" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="12">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="H26" s="8">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="I26" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="J26" s="12">
+        <v>0.71319999999999995</v>
+      </c>
+      <c r="K26" s="12">
+        <v>0.56830000000000003</v>
+      </c>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+    </row>
+    <row r="27" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <v>8</v>
+      </c>
+      <c r="B27" s="12">
+        <v>0</v>
+      </c>
+      <c r="C27" s="12">
+        <v>0.4118</v>
+      </c>
+      <c r="D27" s="12">
+        <v>0.76959999999999995</v>
+      </c>
+      <c r="E27" s="12">
+        <v>0.82040000000000002</v>
+      </c>
+      <c r="F27" s="12">
+        <v>1</v>
+      </c>
+      <c r="G27" s="12">
+        <v>1</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="I27" s="13">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="J27" s="12">
+        <v>0.88049999999999995</v>
+      </c>
+      <c r="K27" s="12">
+        <v>0.82240000000000002</v>
+      </c>
+      <c r="P27" s="6"/>
+    </row>
+    <row r="28" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12">
+        <v>9</v>
+      </c>
+      <c r="B28" s="8">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0.73050000000000004</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.79369999999999996</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="I28" s="8">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="J28" s="8">
+        <v>0.80330000000000001</v>
+      </c>
+      <c r="K28" s="8">
+        <v>0.91300000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="8">
+        <f>AVERAGE(B19:B28)</f>
+        <v>0.24414000000000002</v>
+      </c>
+      <c r="C29" s="8">
+        <f t="shared" ref="C29:K29" si="1">AVERAGE(C19:C28)</f>
+        <v>0.45451000000000008</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" si="1"/>
+        <v>0.75400999999999985</v>
+      </c>
+      <c r="E29" s="8">
+        <f t="shared" si="1"/>
+        <v>0.80105999999999999</v>
+      </c>
+      <c r="F29" s="8">
+        <f>AVERAGE(F19:F28)</f>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="G29" s="8">
+        <f t="shared" si="1"/>
+        <v>0.8083300000000001</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="1"/>
+        <v>0.70833999999999997</v>
+      </c>
+      <c r="I29" s="8">
+        <f t="shared" si="1"/>
+        <v>0.85350999999999999</v>
+      </c>
+      <c r="J29" s="8">
+        <f t="shared" si="1"/>
+        <v>0.69516999999999995</v>
+      </c>
+      <c r="K29" s="8">
+        <f t="shared" si="1"/>
+        <v>0.74231999999999998</v>
+      </c>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+    </row>
+    <row r="33" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+    </row>
+    <row r="34" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" s="28"/>
+      <c r="F34" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G34" s="29"/>
+      <c r="H34" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="I34" s="30"/>
+      <c r="J34" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K34" s="28"/>
+    </row>
+    <row r="35" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28"/>
+      <c r="B35" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="15">
+        <v>0</v>
+      </c>
+      <c r="B36" s="15">
+        <v>0</v>
+      </c>
+      <c r="C36" s="15">
+        <v>1</v>
+      </c>
+      <c r="D36" s="15">
+        <v>0.80110000000000003</v>
+      </c>
+      <c r="E36" s="15">
+        <v>0.78190000000000004</v>
+      </c>
+      <c r="F36" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="G36" s="15">
+        <v>1</v>
+      </c>
+      <c r="H36" s="19">
+        <v>1</v>
+      </c>
+      <c r="I36" s="18">
+        <v>1</v>
+      </c>
+      <c r="J36" s="15">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="K36" s="15">
+        <v>0.96199999999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="15">
+        <v>1</v>
+      </c>
+      <c r="B37" s="15">
+        <v>1</v>
+      </c>
+      <c r="C37" s="15">
+        <v>1</v>
+      </c>
+      <c r="D37" s="15">
+        <v>0.77610000000000001</v>
+      </c>
+      <c r="E37" s="15">
+        <v>0.79059999999999997</v>
+      </c>
+      <c r="F37" s="15">
+        <v>1</v>
+      </c>
+      <c r="G37" s="15">
+        <v>1</v>
+      </c>
+      <c r="H37" s="19">
+        <v>1</v>
+      </c>
+      <c r="I37" s="18">
+        <v>1</v>
+      </c>
+      <c r="J37" s="15">
+        <v>0.95579999999999998</v>
+      </c>
+      <c r="K37" s="15">
+        <v>0.95579999999999998</v>
+      </c>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+    </row>
+    <row r="38" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="15">
+        <v>2</v>
+      </c>
+      <c r="B38" s="15">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="C38" s="15">
+        <v>1</v>
+      </c>
+      <c r="D38" s="15">
+        <v>0.78939999999999999</v>
+      </c>
+      <c r="E38" s="15">
+        <v>0.75109999999999999</v>
+      </c>
+      <c r="F38" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="G38" s="17">
+        <v>1</v>
+      </c>
+      <c r="H38" s="19">
+        <v>0</v>
+      </c>
+      <c r="I38" s="18">
+        <v>1</v>
+      </c>
+      <c r="J38" s="15">
+        <v>0.18959999999999999</v>
+      </c>
+      <c r="K38" s="15">
+        <v>0.96540000000000004</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="15">
+        <v>3</v>
+      </c>
+      <c r="B39" s="15">
+        <v>1</v>
+      </c>
+      <c r="C39" s="15">
+        <v>1</v>
+      </c>
+      <c r="D39" s="15">
+        <v>0.77159999999999995</v>
+      </c>
+      <c r="E39" s="15">
+        <v>0.76890000000000003</v>
+      </c>
+      <c r="F39" s="15">
+        <v>0</v>
+      </c>
+      <c r="G39" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="H39" s="19">
+        <v>1</v>
+      </c>
+      <c r="I39" s="18">
+        <v>1</v>
+      </c>
+      <c r="J39" s="15">
+        <v>0.18459999999999999</v>
+      </c>
+      <c r="K39" s="15">
+        <v>0.17749999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="15">
+        <v>4</v>
+      </c>
+      <c r="B40" s="15">
+        <v>1</v>
+      </c>
+      <c r="C40" s="15">
+        <v>1</v>
+      </c>
+      <c r="D40" s="15">
+        <v>0.77849999999999997</v>
+      </c>
+      <c r="E40" s="15">
+        <v>0.77569999999999995</v>
+      </c>
+      <c r="F40" s="15">
+        <v>1</v>
+      </c>
+      <c r="G40" s="15">
+        <v>1</v>
+      </c>
+      <c r="H40" s="19">
+        <v>1</v>
+      </c>
+      <c r="I40" s="18">
+        <v>1</v>
+      </c>
+      <c r="J40" s="15">
+        <v>0.95609999999999995</v>
+      </c>
+      <c r="K40" s="15">
+        <v>0.95609999999999995</v>
+      </c>
+      <c r="R40" s="6"/>
+    </row>
+    <row r="41" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="15">
+        <v>5</v>
+      </c>
+      <c r="B41" s="15">
+        <v>1</v>
+      </c>
+      <c r="C41" s="15">
+        <v>1</v>
+      </c>
+      <c r="D41" s="15">
+        <v>0.77</v>
+      </c>
+      <c r="E41" s="15">
+        <v>0.75239999999999996</v>
+      </c>
+      <c r="F41" s="15">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="G41" s="15">
+        <v>1</v>
+      </c>
+      <c r="H41" s="19">
+        <v>1</v>
+      </c>
+      <c r="I41" s="18">
+        <v>1</v>
+      </c>
+      <c r="J41" s="15">
+        <v>0.2011</v>
+      </c>
+      <c r="K41" s="15">
+        <v>0.96279999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="15">
+        <v>6</v>
+      </c>
+      <c r="B42" s="15">
+        <v>1</v>
+      </c>
+      <c r="C42" s="15">
+        <v>1</v>
+      </c>
+      <c r="D42" s="15">
+        <v>0.70140000000000002</v>
+      </c>
+      <c r="E42" s="15">
+        <v>0.79339999999999999</v>
+      </c>
+      <c r="F42" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G42" s="15">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="H42" s="19">
+        <v>1</v>
+      </c>
+      <c r="I42" s="18">
+        <v>1</v>
+      </c>
+      <c r="J42" s="15">
+        <v>0.48420000000000002</v>
+      </c>
+      <c r="K42" s="15">
+        <v>0.57050000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="15">
+        <v>7</v>
+      </c>
+      <c r="B43" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="C43" s="15">
+        <v>1</v>
+      </c>
+      <c r="D43" s="15">
+        <v>0.7974</v>
+      </c>
+      <c r="E43" s="15">
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="F43" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G43" s="15">
+        <v>1</v>
+      </c>
+      <c r="H43" s="19">
+        <v>1</v>
+      </c>
+      <c r="I43" s="18">
+        <v>1</v>
+      </c>
+      <c r="J43" s="15">
+        <v>0.41120000000000001</v>
+      </c>
+      <c r="K43" s="15">
+        <v>0.95789999999999997</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15">
+        <v>8</v>
+      </c>
+      <c r="B44" s="15">
+        <v>1</v>
+      </c>
+      <c r="C44" s="15">
+        <v>1</v>
+      </c>
+      <c r="D44" s="15">
+        <v>0.81399999999999995</v>
+      </c>
+      <c r="E44" s="15">
+        <v>0.81620000000000004</v>
+      </c>
+      <c r="F44" s="15">
+        <v>1</v>
+      </c>
+      <c r="G44" s="15">
+        <v>1</v>
+      </c>
+      <c r="H44" s="19">
+        <v>1</v>
+      </c>
+      <c r="I44" s="18">
+        <v>1</v>
+      </c>
+      <c r="J44" s="15">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="K44" s="15">
+        <v>0.81489999999999996</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="15">
+        <v>9</v>
+      </c>
+      <c r="B45" s="8">
+        <v>1</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+      <c r="D45" s="8">
+        <v>0.78380000000000005</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.7712</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G45" s="8">
+        <v>1</v>
+      </c>
+      <c r="H45" s="19">
+        <v>1</v>
+      </c>
+      <c r="I45" s="19">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8">
+        <v>0.1963</v>
+      </c>
+      <c r="K45" s="8">
+        <v>0.95840000000000003</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="8">
+        <f>AVERAGE(B36:B45)</f>
+        <v>0.7916700000000001</v>
+      </c>
+      <c r="C46" s="8">
+        <f t="shared" ref="C46:K46" si="2">AVERAGE(C36:C45)</f>
+        <v>1</v>
+      </c>
+      <c r="D46" s="8">
+        <f t="shared" si="2"/>
+        <v>0.77832999999999997</v>
+      </c>
+      <c r="E46" s="8">
+        <f t="shared" si="2"/>
+        <v>0.78024000000000004</v>
+      </c>
+      <c r="F46" s="8">
+        <f>AVERAGE(F36:F45)</f>
+        <v>0.5416700000000001</v>
+      </c>
+      <c r="G46" s="8">
+        <f>AVERAGE(G36:G45)</f>
+        <v>0.9333300000000001</v>
+      </c>
+      <c r="H46" s="19">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="I46" s="19">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J46" s="8">
+        <f t="shared" si="2"/>
+        <v>0.49587999999999993</v>
+      </c>
+      <c r="K46" s="8">
+        <f t="shared" si="2"/>
+        <v>0.82812999999999981</v>
+      </c>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
+    </row>
+    <row r="47" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="Q47" s="6"/>
+    </row>
+    <row r="48" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="28"/>
+      <c r="F49" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="29"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K49" s="28"/>
+    </row>
+    <row r="50" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="28"/>
+      <c r="B50" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="F50" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G50" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="K50" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="23">
+        <v>0</v>
+      </c>
+      <c r="B51" s="23">
+        <v>1</v>
+      </c>
+      <c r="C51" s="23">
+        <v>1</v>
+      </c>
+      <c r="D51" s="23">
+        <v>0.77769999999999995</v>
+      </c>
+      <c r="E51" s="23">
+        <v>0.77769999999999995</v>
+      </c>
+      <c r="F51" s="23">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="G51" s="23">
+        <v>1</v>
+      </c>
+      <c r="H51" s="19"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="23">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="K51" s="23">
+        <v>0.96199999999999997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="23">
+        <v>1</v>
+      </c>
+      <c r="B52" s="23">
+        <v>1</v>
+      </c>
+      <c r="C52" s="23">
+        <v>1</v>
+      </c>
+      <c r="D52" s="23">
+        <v>0.77610000000000001</v>
+      </c>
+      <c r="E52" s="23">
+        <v>0.79059999999999997</v>
+      </c>
+      <c r="F52" s="23">
+        <v>1</v>
+      </c>
+      <c r="G52" s="23">
+        <v>1</v>
+      </c>
+      <c r="H52" s="19"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="23">
+        <v>0.95579999999999998</v>
+      </c>
+      <c r="K52" s="23">
+        <v>0.95579999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="23">
+        <v>2</v>
+      </c>
+      <c r="B53" s="23">
+        <v>1</v>
+      </c>
+      <c r="C53" s="23">
+        <v>1</v>
+      </c>
+      <c r="D53" s="23">
+        <v>0.74919999999999998</v>
+      </c>
+      <c r="E53" s="23">
+        <v>0.77710000000000001</v>
+      </c>
+      <c r="F53" s="23">
+        <v>1</v>
+      </c>
+      <c r="G53" s="23">
+        <v>1</v>
+      </c>
+      <c r="H53" s="19"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="23">
+        <v>0.96540000000000004</v>
+      </c>
+      <c r="K53" s="23">
+        <v>0.96540000000000004</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="23">
+        <v>3</v>
+      </c>
+      <c r="B54" s="23">
+        <v>0</v>
+      </c>
+      <c r="C54" s="23">
+        <v>1</v>
+      </c>
+      <c r="D54" s="23">
+        <v>0.76949999999999996</v>
+      </c>
+      <c r="E54" s="23">
+        <v>0.78680000000000005</v>
+      </c>
+      <c r="F54" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="G54" s="23">
+        <v>1</v>
+      </c>
+      <c r="H54" s="19"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="23">
+        <v>0.17680000000000001</v>
+      </c>
+      <c r="K54" s="23">
+        <v>0.95599999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="23">
+        <v>4</v>
+      </c>
+      <c r="B55" s="23">
+        <v>1</v>
+      </c>
+      <c r="C55" s="23">
+        <v>1</v>
+      </c>
+      <c r="D55" s="23">
+        <v>0.77569999999999995</v>
+      </c>
+      <c r="E55" s="23">
+        <v>0.77569999999999995</v>
+      </c>
+      <c r="F55" s="23">
+        <v>1</v>
+      </c>
+      <c r="G55" s="23">
+        <v>1</v>
+      </c>
+      <c r="H55" s="19"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="23">
+        <v>0.95609999999999995</v>
+      </c>
+      <c r="K55" s="23">
+        <v>0.95609999999999995</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="23">
+        <v>5</v>
+      </c>
+      <c r="B56" s="23">
+        <v>1</v>
+      </c>
+      <c r="C56" s="23">
+        <v>1</v>
+      </c>
+      <c r="D56" s="23">
+        <v>0.77</v>
+      </c>
+      <c r="E56" s="23">
+        <v>0.77</v>
+      </c>
+      <c r="F56" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="G56" s="23">
+        <v>1</v>
+      </c>
+      <c r="H56" s="19"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="23">
+        <v>0.2011</v>
+      </c>
+      <c r="K56" s="23">
+        <v>0.2011</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="23">
+        <v>6</v>
+      </c>
+      <c r="B57" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="C57" s="23">
+        <v>1</v>
+      </c>
+      <c r="D57" s="23">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="E57" s="23">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="F57" s="23">
+        <v>1</v>
+      </c>
+      <c r="G57" s="23">
+        <v>1</v>
+      </c>
+      <c r="H57" s="19"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="23">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="K57" s="23">
+        <v>0.58599999999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="23">
+        <v>7</v>
+      </c>
+      <c r="B58" s="23">
+        <v>0</v>
+      </c>
+      <c r="C58" s="23">
+        <v>1</v>
+      </c>
+      <c r="D58" s="23">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="E58" s="23">
+        <v>0.79579999999999995</v>
+      </c>
+      <c r="F58" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="G58" s="23">
+        <v>1</v>
+      </c>
+      <c r="H58" s="19"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="23">
+        <v>0.70089999999999997</v>
+      </c>
+      <c r="K58" s="23">
+        <v>0.95789999999999997</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="23">
+        <v>8</v>
+      </c>
+      <c r="B59" s="23">
+        <v>1</v>
+      </c>
+      <c r="C59" s="23">
+        <v>1</v>
+      </c>
+      <c r="D59" s="23">
+        <v>0.81620000000000004</v>
+      </c>
+      <c r="E59" s="23">
+        <v>0.81620000000000004</v>
+      </c>
+      <c r="F59" s="23">
+        <v>1</v>
+      </c>
+      <c r="G59" s="23">
+        <v>1</v>
+      </c>
+      <c r="H59" s="19"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="23">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="K59" s="23">
+        <v>0.81489999999999996</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="23">
+        <v>9</v>
+      </c>
+      <c r="B60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="C60" s="8">
+        <v>1</v>
+      </c>
+      <c r="D60" s="8">
+        <v>0.65229999999999999</v>
+      </c>
+      <c r="E60" s="8">
+        <v>0.7712</v>
+      </c>
+      <c r="F60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G60" s="8">
+        <v>1</v>
+      </c>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="8">
+        <v>0.18049999999999999</v>
+      </c>
+      <c r="K60" s="8">
+        <v>0.95840000000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61" s="8">
+        <f>AVERAGE(B51:B60)</f>
+        <v>0.7</v>
+      </c>
+      <c r="C61" s="8">
+        <f t="shared" ref="C61:K61" si="3">AVERAGE(C51:C60)</f>
+        <v>1</v>
+      </c>
+      <c r="D61" s="8">
+        <f t="shared" si="3"/>
+        <v>0.76886999999999994</v>
+      </c>
+      <c r="E61" s="8">
+        <f t="shared" si="3"/>
+        <v>0.7858099999999999</v>
+      </c>
+      <c r="F61" s="8">
+        <f>AVERAGE(F51:F60)</f>
+        <v>0.74167000000000005</v>
+      </c>
+      <c r="G61" s="8">
+        <f>AVERAGE(G51:G60)</f>
+        <v>1</v>
+      </c>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="8">
+        <f t="shared" si="3"/>
+        <v>0.64995000000000003</v>
+      </c>
+      <c r="K61" s="8">
+        <f t="shared" si="3"/>
+        <v>0.83135999999999988</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA574D9-6098-4E7A-94F4-A2DD9F4FC518}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="16.77734375" defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="16.77734375" style="14"/>
+    <col min="3" max="3" width="24" style="14" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="14" customWidth="1"/>
+    <col min="5" max="5" width="25.21875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" style="27" customWidth="1"/>
+    <col min="9" max="9" width="24.88671875" style="14" customWidth="1"/>
+    <col min="10" max="16384" width="16.77734375" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="J4" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="27" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27">
+        <v>4</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="27">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" s="14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="15" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="27">
+        <v>6</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="27"/>
+      <c r="I8" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="J8" s="15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="27">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/test/实验数据.xlsx
+++ b/test/实验数据.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mylife_yanjiu\project\rag_sva\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E70923-396E-41B3-8347-6E03F5F17E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAB8FEC-DC42-4C95-978B-1A7FE82D445C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,13 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="252">
   <si>
     <t>设计</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脆弱性评估</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1175,51 +1171,695 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>7/5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7/7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Method</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识库类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>g21：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1阶优化RAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_all_h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>7/6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7/5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7/3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7/1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7/4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7/7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Method</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>知识库类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>g21：</t>
+    <t>/GPT-5mini</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_4_o5m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_3_o5m</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Retrieval-augmented generation for knowledge-intensive
+NLP tasks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文献名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相关性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提出RAG概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LLM-based and retrieval-augmented control code
+generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG应用于代码生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Benchmarking retrieval-
+augmented generation for medicine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG应用于医疗领域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LLM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BERT: Pre-training
+of deep bidirectional transformers for language understanding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bert模型提出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">GPT-4 Technical Report </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPT-4模型，在多模态，复杂推理任务上的进步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeepSeek-R1: Incentivizing Reasoning Capability in LLMs via Reinforcement Learning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deepseek-R1，强化学习提高LLM推理能力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hybrid Retrieval for Hallucination
+Mitigation in Large Language Models: A
+Comparative Analysis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混合检索RAG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Retrieval-Augmented Generation for Large Language Models: A Survey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>介绍简单RAG以及高级RAG等概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>From Code Generation to Software Testing: AI Copilot With Context-Based Retrieval-Augmented Generation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG应用于软件测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attention is All You Need</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{koziolek2024llm,
+  title={LLM-based and retrieval-augmented control code generation},
+  author={Koziolek, Heiko and Gr{\"u}ner, Sten and Hark, Rhaban and Ashiwal, Virendra and Linsbauer, Sofia and Eskandani, Nafise},
+  booktitle={Proceedings of the 1st International Workshop on Large Language Models for Code},
+  pages={22--29},
+  year={2024}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将RAG系统应用于工业控制代码生成领域，已解决专业知识的集成问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{xiong2024benchmarking,
+  title={Benchmarking retrieval-augmented generation for medicine},
+  author={Xiong, Guangzhi and Jin, Qiao and Lu, Zhiyong and Zhang, Aidong},
+  booktitle={Findings of the Association for Computational Linguistics: ACL 2024},
+  pages={6233--6251},
+  year={2024}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{wang2025code,
+  title={From code generation to software testing: AI Copilot with context-based RAG},
+  author={Wang, Yuchen and Guo, Shangxin and Tan, Chee Wei},
+  journal={IEEE Software},
+  year={2025},
+  publisher={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{lewis2020retrieval,
+  title={Retrieval-augmented generation for knowledge-intensive nlp tasks},
+  author={Lewis, Patrick and Perez, Ethan and Piktus, Aleksandra and Petroni, Fabio and Karpukhin, Vladimir and Goyal, Naman and K{\"u}ttler, Heinrich and Lewis, Mike and Yih, Wen-tau and Rockt{\"a}schel, Tim and others},
+  journal={Advances in neural information processing systems},
+  volume={33},
+  pages={9459--9474},
+  year={2020}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{vaswani2017attention,
+  title={Attention is all you need},
+  author={Vaswani, Ashish and Shazeer, Noam and Parmar, Niki and Uszkoreit, Jakob and Jones, Llion and Gomez, Aidan N and Kaiser, {\L}ukasz and Polosukhin, Illia},
+  journal={Advances in neural information processing systems},
+  volume={30},
+  year={2017}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{gao2023retrieval,
+  title={Retrieval-augmented generation for large language models: A survey},
+  author={Gao, Yunfan and Xiong, Yun and Gao, Xinyu and Jia, Kangxiang and Pan, Jinliu and Bi, Yuxi and Dai, Yixin and Sun, Jiawei and Wang, Haofen and Wang, Haofen and others},
+  journal={arXiv preprint arXiv:2312.10997},
+  volume={2},
+  number={1},
+  pages={32},
+  year={2023}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{mala2025hybrid,
+  title={Hybrid retrieval for hallucination mitigation in large language models: A comparative analysis},
+  author={Mala, Chandana Sree and Gezici, Gizem and Giannotti, Fosca},
+  journal={arXiv preprint arXiv:2504.05324},
+  year={2025}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{guo2025deepseek,
+  title={Deepseek-r1: Incentivizing reasoning capability in llms via reinforcement learning},
+  author={Guo, Daya and Yang, Dejian and Zhang, Haowei and Song, Junxiao and Wang, Peiyi and Zhu, Qihao and Xu, Runxin and Zhang, Ruoyu and Ma, Shirong and Bi, Xiao and others},
+  journal={arXiv preprint arXiv:2501.12948},
+  year={2025}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{achiam2023gpt,
+  title={Gpt-4 technical report},
+  author={Achiam, Josh and Adler, Steven and Agarwal, Sandhini and Ahmad, Lama and Akkaya, Ilge and Aleman, Florencia Leoni and Almeida, Diogo and Altenschmidt, Janko and Altman, Sam and Anadkat, Shyamal and others},
+  journal={arXiv preprint arXiv:2303.08774},
+  year={2023}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{devlin2019bert,
+  title={Bert: Pre-training of deep bidirectional transformers for language understanding},
+  author={Devlin, Jacob and Chang, Ming-Wei and Lee, Kenton and Toutanova, Kristina},
+  booktitle={Proceedings of the 2019 conference of the North American chapter of the association for computational linguistics: human language technologies, volume 1 (long and short papers)},
+  pages={4171--4186},
+  year={2019}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{vasudevan2010goldmine,
+  title={Goldmine: Automatic assertion generation using data mining and static analysis},
+  author={Vasudevan, Shobha and Sheridan, David and Patel, Sanjay and Tcheng, David and Tuohy, Bill and Johnson, Daniel},
+  booktitle={2010 Design, Automation \&amp; Test in Europe Conference \&amp; Exhibition (DATE 2010)},
+  pages={626--629},
+  year={2010},
+  organization={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Goldmine: Automatic assertion generation using data mining and static analysis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HARM: A Hint-Based Assertion Miner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{germiniani2022harm,
+  title={Harm: a hint-based assertion miner},
+  author={Germiniani, Samuele and Pravadelli, Graziano},
+  journal={IEEE Transactions on Computer-Aided Design of Integrated Circuits and Systems},
+  volume={41},
+  number={11},
+  pages={4277--4288},
+  year={2022},
+  publisher={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安全</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Llm-guided formal verification coupled with mutation testing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{hassan2024llm,
+  title={Llm-guided formal verification coupled with mutation testing},
+  author={Hassan, Muhammad and Ahmadi-Pour, Sallar and Qayyum, Khushboo and Jha, Chandan Kumar and Drechsler, Rolf},
+  booktitle={2024 Design, Automation \&amp; Test in Europe Conference \&amp; Exhibition (DATE)},
+  pages={1--2},
+  year={2024},
+  organization={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Security) Assertions by Large Language Models</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{kande2024security,
+  title={(Security) assertions by large language models},
+  author={Kande, Rahul and Pearce, Hammond and Tan, Benjamin and Dolan-Gavitt, Brendan and Thakur, Shailja and Karri, Ramesh and Rajendran, Jeyavijayan},
+  journal={IEEE Transactions on Information Forensics and Security},
+  volume={19},
+  pages={4374--4389},
+  year={2024},
+  publisher={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LASP: LLM Assisted Security Property Generation for SoC Verification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{ayalasomayajula2024lasp,
+  title={Lasp: Llm assisted security property generation for soc verification},
+  author={Ayalasomayajula, Avinash and Guo, Rui and Zhou, Jingbo and Saha, Sujan Kumar and Farahmandi, Farimah},
+  booktitle={Proceedings of the 2024 ACM/IEEE International Symposium on Machine Learning for CAD},
+  pages={1--7},
+  year={2024}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OpenAssert: Towards Secure Assertion Generation using Large Language Models</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{menon2025openassert,
+  title={Openassert: Towards secure assertion generation using large language models},
+  author={Menon, Anand and Miftah, Samit Shahnawaz and Srivastava, Amisha and Kundu, Shamik and Kundu, Shovik and Raha, Arnab and Banerjee, Suvadeep and Mathaikutty, Deepak and Basu, Kanad},
+  booktitle={2025 IEEE 43rd VLSI Test Symposium (VTS)},
+  pages={1--5},
+  year={2025},
+  organization={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LASSO: LLM-Aided Security Property Generation
+for Assertion-based SoC Verification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{ankireddy2025lasso,
+  title={LASSO: LLM-Aided Security Property Generation for Assertion-based SoC Verification},
+  author={Ankireddy, Dinesh Reddy and Paria, Sudipta and Dasgupta, Aritra and Ray, Sandip and Bhunia, Swarup},
+  booktitle={2025 ACM/IEEE 7th Symposium on Machine Learning for CAD (MLCAD)},
+  pages={1--10},
+  year={2025},
+  organization={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{fang2024assertllm,
+  title={Assertllm: Generating and evaluating hardware verification assertions from design specifications via multi-llms},
+  author={Fang, Wenji and Li, Mengming and Li, Min and Yan, Zhiyuan and Liu, Shang and Xie, Zhiyao and Zhang, Hongce},
+  journal={arXiv preprint arXiv:2402.00386},
+  year={2024}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assertllm: Generating and evaluating hardware verification assertions from design specifications via multi-llms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Special Session: ThreatLens: LLM-guided Threat
+Modeling and Test Plan Generation for Hardware
+Security Verification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{saha2025threatlens,
+  title={Threatlens: Llm-guided threat modeling and test plan generation for hardware security verification},
+  author={Saha, Dipayan and Shaikh, Hasan Al and Tarek, Shams and Farahmandi, Farimah},
+  journal={arXiv preprint arXiv:2505.06821},
+  year={2025}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">A Survey on Hardware Security: Current Trends and Challenges </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综述，硬件安全与漏洞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{akter2023survey,
+  title={A survey on hardware security: Current trends and challenges},
+  author={Akter, Sonia and Khalil, Kasem and Bayoumi, Magdy},
+  journal={IEEe Access},
+  volume={11},
+  pages={77543--77565},
+  year={2023},
+  publisher={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">The Emergence of Hardware Fuzzing: A Critical Review of its Significance </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综述，模糊测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{saravanan2024emergence,
+  title={The emergence of hardware fuzzing: A critical review of its significance},
+  author={Saravanan, Raghul and Dinakarrao, Sai Manoj Pudukotai},
+  journal={arXiv preprint arXiv:2403.12812},
+  year={2024}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A Survey on Assertion-based Hardware Verification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综述，ABV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{witharana2022survey,
+  title={A survey on assertion-based hardware verification},
+  author={Witharana, Hasini and Lyu, Yangdi and Charles, Subodha and Mishra, Prabhat},
+  journal={ACM Computing Surveys (CSUR)},
+  volume={54},
+  number={11s},
+  pages={1--33},
+  year={2022},
+  publisher={ACM New York, NY}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{hu2020overview,
+  title={An overview of hardware security and trust: Threats, countermeasures, and design tools},
+  author={Hu, Wei and Chang, Chip-Hong and Sengupta, Anirban and Bhunia, Swarup and Kastner, Ryan and Li, Hai},
+  journal={IEEE Transactions on Computer-Aided Design of Integrated Circuits and Systems},
+  volume={40},
+  number={6},
+  pages={1010--1038},
+  year={2020},
+  publisher={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">An Overview of Hardware Security and Trust: Threats, Countermeasures and Design Tools </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综述，硬件安全等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Automatic SystemVerilog Assertion Generation: Challenges and Opportunities</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{afsharmazayejani2025automatic,
+  title={Automatic SystemVerilog Assertion Generation: Challenges and Opportunities},
+  author={Afsharmazayejani, Raheel and Pearce, Hammond and Tan, Benjamin},
+  booktitle={2025 IEEE Canadian Conference on Electrical and Computer Engineering (CCECE)},
+  pages={576--581},
+  year={2025},
+  organization={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LLM-Assisted Circuit Verification: A Comprehensive Survey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综述，LLM应用安全SVA生成的挑战与机遇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综述，LLM应用电路验证的挑战与机遇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{liu2026llm,
+  title={LLM-Assisted Circuit Verification: A Comprehensive Survey},
+  author={Liu, Hongduo and Lu, Yuntao and Wang, Mingjun and Yao, Xufeng and Yu, Bei},
+  booktitle={2026 31st Asia and South Pacific Design Automation Conference (ASP-DAC)},
+  pages={439--446},
+  year={2026},
+  organization={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Towards Property Driven Hardware Security</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{hu2016towards,
+  title={Towards property driven hardware security},
+  author={Hu, Wei and Althoff, Alric and Ardeshiricham, Armaiti and Kastner, Ryan},
+  booktitle={2016 17th International Workshop on Microprocessor and SOC Test and Verification (MTV)},
+  pages={51--56},
+  year={2016},
+  organization={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综述，安全属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{restuccia2021aker,
+  title={Aker: A design and verification framework for safe and secure soc access control},
+  author={Restuccia, Francesco and Meza, Andres and Kastner, Ryan},
+  booktitle={2021 IEEE/ACM International Conference On Computer Aided Design (ICCAD)},
+  pages={1--9},
+  year={2021},
+  organization={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Aker: A Design and Verification Framework for Safe and Secure SoC Access Control </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>访问控制漏洞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Processor Hardware Security Vulnerabilities and their Detection by Unique Program Execution Checking</t>
+  </si>
+  <si>
+    <t>UPEC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{fadiheh2019processor,
+  title={Processor hardware security vulnerabilities and their detection by unique program execution checking},
+  author={Fadiheh, Mohammad Rahmani and Stoffel, Dominik and Barrett, Clark and Mitra, Subhasish and Kunz, Wolfgang},
+  booktitle={2019 Design, Automation \&amp; Test in Europe Conference \&amp; Exhibition (DATE)},
+  pages={994--999},
+  year={2019},
+  organization={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A Survey on Machine Learning Against Hardware Trojan Attacks: Recent Advances and Challenges</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬件木马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{huang2020survey,
+  title={A survey on machine learning against hardware trojan attacks: Recent advances and challenges},
+  author={Huang, Zhao and Wang, Quan and Chen, Yin and Jiang, Xiaohong},
+  journal={IEEE Access},
+  volume={8},
+  pages={10796--10826},
+  year={2020},
+  publisher={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HardFails: Insights into Software-Exploitable Hardware Bugs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hardfail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@inproceedings{dessouky2019hardfails,
+  title={$\{$HardFails$\}$: insights into $\{$software-exploitable$\}$ hardware bugs},
+  author={Dessouky, Ghada and Gens, David and Haney, Patrick and Persyn, Garrett and Kanuparthi, Arun and Khattri, Hareesh and Fung, Jason M and Sadeghi, Ahmad-Reza and Rajendran, Jeyavijayan},
+  booktitle={28th USENIX Security Symposium (USENIX Security 19)},
+  pages={213--230},
+  year={2019}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoC Security Verification using Property Checking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@incollection{farahmandi2019soc,
+  title={SoC security verification using property checking},
+  author={Farahmandi, Farimah and Huang, Yuanwen and Mishra, Prabhat},
+  booktitle={System-on-Chip Security: Validation and Verification},
+  pages={137--152},
+  year={2019},
+  publisher={Springer}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性检查，断言检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Mining hardware assertions with guidance from static analysis </t>
+  </si>
+  <si>
+    <t>断言生成，静态技术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>`@article{hertz2013mining,
+  title={Mining hardware assertions with guidance from static analysis},
+  author={Hertz, Samuel and Sheridan, David and Vasudevan, Shobha},
+  journal={IEEE Transactions on Computer-Aided Design of Integrated Circuits and Systems},
+  volume={32},
+  number={6},
+  pages={952--965},
+  year={2013},
+  publisher={IEEE}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bge m3-embedding: Multi-lingual, multi-functionality, multi-granularity text embeddings through self-knowledge distillation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bge-m3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Milvus: A purpose-built vector data management system</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1299,7 +1939,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1346,12 +1986,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1382,14 +2016,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1671,257 +2305,476 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="18.77734375" defaultRowHeight="28.05" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="18.77734375" style="10"/>
+    <col min="1" max="1" width="18.77734375" style="8"/>
+    <col min="2" max="2" width="39.6640625" style="8" customWidth="1"/>
+    <col min="3" max="5" width="18.77734375" style="8"/>
+    <col min="6" max="6" width="29.109375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="36.109375" style="8" customWidth="1"/>
+    <col min="8" max="8" width="37.6640625" style="8" customWidth="1"/>
+    <col min="9" max="16384" width="18.77734375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-    </row>
-    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E2" s="8">
+        <v>2020</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="B3" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2020</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="B6" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2023</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
-        <v>0</v>
-      </c>
-      <c r="B3" s="10">
-        <v>0.3125</v>
-      </c>
-      <c r="C3" s="10">
-        <v>0.77400000000000002</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0.59589999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
-        <v>1</v>
-      </c>
-      <c r="B4" s="10">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C4" s="10">
-        <v>0.7863</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.86670000000000003</v>
-      </c>
-      <c r="E4" s="10">
-        <v>1</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0.40150000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="B7" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="8">
+        <v>2025</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2025</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2023</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2025</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="8">
+        <v>2017</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2010</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
         <v>2</v>
       </c>
-      <c r="B5" s="10">
-        <v>0.2273</v>
-      </c>
-      <c r="C5" s="10">
-        <v>0.83230000000000004</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10">
-        <v>0.58850000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
-        <v>3</v>
-      </c>
-      <c r="B6" s="10">
-        <v>0.625</v>
-      </c>
-      <c r="C6" s="10">
-        <v>0.79710000000000003</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0.50470000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10">
-        <v>0.30559999999999998</v>
-      </c>
-      <c r="C7" s="10">
-        <v>0.78910000000000002</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.95</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0.83330000000000004</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0.75729999999999997</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>5</v>
-      </c>
-      <c r="B8" s="10">
-        <v>0</v>
-      </c>
-      <c r="C8" s="10">
-        <v>0.78080000000000005</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0.875</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0.40389999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>6</v>
-      </c>
-      <c r="B9" s="10">
-        <v>0.13789999999999999</v>
-      </c>
-      <c r="C9" s="10">
-        <v>0.79020000000000001</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.67920000000000003</v>
-      </c>
-      <c r="E9" s="10">
-        <v>0</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0.62270000000000003</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
-        <v>7</v>
-      </c>
-      <c r="B10" s="10">
-        <v>9.5200000000000007E-2</v>
-      </c>
-      <c r="C10" s="10">
-        <v>0.7681</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="F10" s="10">
-        <v>0.622</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>8</v>
-      </c>
-      <c r="B11" s="10">
-        <v>4.3499999999999997E-2</v>
-      </c>
-      <c r="C11" s="10">
-        <v>0.79330000000000001</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="F11" s="10">
-        <v>0.48809999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
-        <v>9</v>
-      </c>
-      <c r="B12" s="10">
-        <v>0.17299999999999999</v>
-      </c>
-      <c r="C12" s="10">
-        <v>0.77700000000000002</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="F12" s="10">
-        <v>0.68079999999999996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="4:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="1"/>
+      <c r="B16" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2022</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="8">
+        <v>2023</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2022</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E22" s="8">
+        <v>2020</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2025</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E24" s="8">
+        <v>2026</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2016</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2019</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2021</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2019</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2020</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E31" s="8">
+        <v>2019</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="E33" s="8">
+        <v>2013</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="E34" s="8">
+        <v>2024</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E35" s="8">
+        <v>2021</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:F1"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1929,7 +2782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF19DE99-23A4-44BD-B675-0AE246CEEB40}">
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr defaultColWidth="18.77734375" defaultRowHeight="28.05" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="18.77734375" style="2"/>
@@ -1937,39 +2790,39 @@
   <sheetData>
     <row r="1" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>11</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>12</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
       <c r="K1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -1977,22 +2830,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="F2" s="8">
         <v>0.4</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -2005,16 +2858,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="F3" s="8">
         <v>0.4</v>
@@ -2024,7 +2877,7 @@
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K3" s="8">
         <v>100</v>
@@ -2035,16 +2888,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="8">
         <v>0.4</v>
@@ -2063,16 +2916,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="8">
         <v>0.4</v>
@@ -2091,16 +2944,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" s="8">
         <v>0.4</v>
@@ -2110,7 +2963,7 @@
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K6" s="8">
         <v>100</v>
@@ -2121,16 +2974,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" s="8">
         <v>0.4</v>
@@ -2150,119 +3003,119 @@
     </row>
     <row r="10" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="D11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="J12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="N12" s="2">
         <v>3</v>
@@ -2270,116 +3123,116 @@
     </row>
     <row r="13" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="K15" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N15" s="2">
         <v>1</v>
@@ -2387,40 +3240,40 @@
     </row>
     <row r="16" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="N16" s="2">
         <v>4</v>
@@ -2428,116 +3281,116 @@
     </row>
     <row r="17" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="H18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="E19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N19" s="2">
         <v>3</v>
@@ -2548,215 +3401,215 @@
     </row>
     <row r="21" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N26" s="2">
         <v>1</v>
@@ -2764,425 +3617,425 @@
     </row>
     <row r="27" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N39" s="2">
         <v>1</v>
@@ -3190,215 +4043,215 @@
     </row>
     <row r="40" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N46" s="2">
         <v>5</v>
@@ -3406,107 +4259,107 @@
     </row>
     <row r="47" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M49" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="J49" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L49" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="N49" s="2">
         <v>2</v>
@@ -3514,485 +4367,611 @@
     </row>
     <row r="50" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C54" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="E54" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K54" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>4</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C55" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="D55" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="20" t="s">
+      <c r="E55" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="H55" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E55" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="F55" s="22" t="s">
+      <c r="I55" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="J55" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="G55" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="H55" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="I55" s="21" t="s">
+      <c r="K55" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="J55" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="K55" s="21" t="s">
+      <c r="L55" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="L55" s="21" t="s">
-        <v>121</v>
-      </c>
       <c r="M55" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>5</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F56" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="H56" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="I56" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="J56" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K56" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C56" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="F56" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="G56" s="21" t="s">
+      <c r="L56" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H56" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I56" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="J56" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="K56" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="M56" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>6</v>
       </c>
-      <c r="B57" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="C57" s="21" t="s">
+      <c r="B57" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="J57" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="K57" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="L57" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D57" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="F57" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="G57" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="H57" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="I57" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="J57" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="K57" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="M57" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>4</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D59" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="E59" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H59" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="J59" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D59" s="20" t="s">
+      <c r="K59" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="E59" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="F59" s="22" t="s">
+      <c r="L59" s="24">
+        <v>0.44290000000000002</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" s="8" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="G59" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="H59" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="I59" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="J59" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="K59" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="L59" s="26">
-        <v>0.44290000000000002</v>
-      </c>
-      <c r="M59" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="N59" s="8" t="s">
+      <c r="C60" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" s="20" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="8">
-        <v>5</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D60" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>140</v>
-      </c>
       <c r="F60" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G60" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="H60" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="I60" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="J60" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="K60" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="L60" s="25">
-        <v>0.61429999999999996</v>
-      </c>
+      <c r="G60" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H60" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="I60" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="J60" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="K60" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="L60" s="24"/>
       <c r="M60" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="N60" s="8" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
+        <v>5</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="I61" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="K61" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L61" s="23">
+        <v>0.77139999999999997</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="8">
         <v>6</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B62" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D62" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="C61" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="F61" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G61" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="H61" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="I61" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="J61" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="K61" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="L61" s="25">
-        <v>0.77139999999999997</v>
-      </c>
-      <c r="M61" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="N61" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>2</v>
-      </c>
-      <c r="B63" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E63" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F63" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="G63" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="H63" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="I63" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="J63" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="K63" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="L63" s="25">
-        <v>0.87139999999999995</v>
-      </c>
-      <c r="N63" s="2" t="s">
-        <v>144</v>
+      <c r="E62" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I62" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="J62" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="K62" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="L62" s="23">
+        <v>0.94289999999999996</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="N62" s="8" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
+        <v>2</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="H64" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I64" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="J64" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="K64" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="L64" s="23">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
         <v>3</v>
       </c>
-      <c r="B64" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="C64" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D64" s="21" t="s">
+      <c r="B65" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G65" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="H65" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I65" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="J65" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="K65" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L65" s="23">
+        <v>0.92859999999999998</v>
+      </c>
+      <c r="N65" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E64" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="F64" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="G64" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="H64" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="I64" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="J64" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="K64" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="L64" s="25">
-        <v>0.92859999999999998</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>143</v>
+    </row>
+    <row r="68" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>2</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F70" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G70" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="H70" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I70" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="J70" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="K70" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L70" s="23">
+        <v>0.95709999999999995</v>
+      </c>
+      <c r="N70" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>3</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="G71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="H71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="J71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="K71" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L71" s="9">
+        <v>1</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4010,77 +4989,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
+      <c r="A1" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
       <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="25"/>
+      <c r="F2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28" t="s">
+      <c r="G2" s="26"/>
+      <c r="H2" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="29"/>
-      <c r="H2" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="28"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
+      <c r="A3" s="25"/>
       <c r="B3" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="D3" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="F3" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="H3" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="J3" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>75</v>
       </c>
       <c r="N3" s="9"/>
     </row>
@@ -4439,7 +5418,7 @@
     </row>
     <row r="14" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" s="8">
         <f>AVERAGE(B4:B13)</f>
@@ -4490,79 +5469,79 @@
       <c r="R14" s="6"/>
     </row>
     <row r="16" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+    </row>
+    <row r="17" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="25"/>
+      <c r="F17" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="26"/>
+      <c r="H17" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="25"/>
+      <c r="M17" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-    </row>
-    <row r="17" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="29"/>
-      <c r="H17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="K17" s="28"/>
-      <c r="M17" s="8" t="s">
-        <v>81</v>
-      </c>
     </row>
     <row r="18" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
+      <c r="A18" s="25"/>
       <c r="B18" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>75</v>
-      </c>
       <c r="D18" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>75</v>
-      </c>
       <c r="F18" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G18" s="12" t="s">
-        <v>75</v>
-      </c>
       <c r="H18" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I18" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="12" t="s">
-        <v>75</v>
-      </c>
       <c r="J18" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
@@ -4934,7 +5913,7 @@
     </row>
     <row r="29" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="8">
         <f>AVERAGE(B19:B28)</f>
@@ -4985,145 +5964,145 @@
       <c r="R29" s="6"/>
     </row>
     <row r="33" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
+      <c r="A33" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
     </row>
     <row r="34" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="25"/>
+      <c r="F34" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28" t="s">
+      <c r="G34" s="26"/>
+      <c r="H34" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="27"/>
+      <c r="J34" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="G34" s="29"/>
-      <c r="H34" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="I34" s="30"/>
-      <c r="J34" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="K34" s="28"/>
+      <c r="K34" s="25"/>
     </row>
     <row r="35" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="15" t="s">
+      <c r="A35" s="25"/>
+      <c r="B35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E35" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G35" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="H35" s="18" t="s">
+      <c r="H35" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I35" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="I35" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="J35" s="15" t="s">
+      <c r="J35" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="K35" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K35" s="15" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="36" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15">
+      <c r="A36" s="14">
         <v>0</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="14">
         <v>0</v>
       </c>
-      <c r="C36" s="15">
-        <v>1</v>
-      </c>
-      <c r="D36" s="15">
+      <c r="C36" s="14">
+        <v>1</v>
+      </c>
+      <c r="D36" s="14">
         <v>0.80110000000000003</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="14">
         <v>0.78190000000000004</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="14">
         <v>0.25</v>
       </c>
-      <c r="G36" s="15">
-        <v>1</v>
-      </c>
-      <c r="H36" s="19">
-        <v>1</v>
-      </c>
-      <c r="I36" s="18">
-        <v>1</v>
-      </c>
-      <c r="J36" s="15">
+      <c r="G36" s="14">
+        <v>1</v>
+      </c>
+      <c r="H36" s="17">
+        <v>1</v>
+      </c>
+      <c r="I36" s="16">
+        <v>1</v>
+      </c>
+      <c r="J36" s="14">
         <v>0.56499999999999995</v>
       </c>
-      <c r="K36" s="15">
+      <c r="K36" s="14">
         <v>0.96199999999999997</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15">
-        <v>1</v>
-      </c>
-      <c r="B37" s="15">
-        <v>1</v>
-      </c>
-      <c r="C37" s="15">
-        <v>1</v>
-      </c>
-      <c r="D37" s="15">
+      <c r="A37" s="14">
+        <v>1</v>
+      </c>
+      <c r="B37" s="14">
+        <v>1</v>
+      </c>
+      <c r="C37" s="14">
+        <v>1</v>
+      </c>
+      <c r="D37" s="14">
         <v>0.77610000000000001</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="14">
         <v>0.79059999999999997</v>
       </c>
-      <c r="F37" s="15">
-        <v>1</v>
-      </c>
-      <c r="G37" s="15">
-        <v>1</v>
-      </c>
-      <c r="H37" s="19">
-        <v>1</v>
-      </c>
-      <c r="I37" s="18">
-        <v>1</v>
-      </c>
-      <c r="J37" s="15">
+      <c r="F37" s="14">
+        <v>1</v>
+      </c>
+      <c r="G37" s="14">
+        <v>1</v>
+      </c>
+      <c r="H37" s="17">
+        <v>1</v>
+      </c>
+      <c r="I37" s="16">
+        <v>1</v>
+      </c>
+      <c r="J37" s="14">
         <v>0.95579999999999998</v>
       </c>
-      <c r="K37" s="15">
+      <c r="K37" s="14">
         <v>0.95579999999999998</v>
       </c>
       <c r="L37" s="6"/>
@@ -5135,253 +6114,253 @@
       <c r="R37" s="6"/>
     </row>
     <row r="38" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15">
+      <c r="A38" s="14">
         <v>2</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="14">
         <v>0.66669999999999996</v>
       </c>
-      <c r="C38" s="15">
-        <v>1</v>
-      </c>
-      <c r="D38" s="15">
+      <c r="C38" s="14">
+        <v>1</v>
+      </c>
+      <c r="D38" s="14">
         <v>0.78939999999999999</v>
       </c>
-      <c r="E38" s="15">
+      <c r="E38" s="14">
         <v>0.75109999999999999</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="14">
         <v>0.25</v>
       </c>
-      <c r="G38" s="17">
-        <v>1</v>
-      </c>
-      <c r="H38" s="19">
+      <c r="G38" s="15">
+        <v>1</v>
+      </c>
+      <c r="H38" s="17">
         <v>0</v>
       </c>
-      <c r="I38" s="18">
-        <v>1</v>
-      </c>
-      <c r="J38" s="15">
+      <c r="I38" s="16">
+        <v>1</v>
+      </c>
+      <c r="J38" s="14">
         <v>0.18959999999999999</v>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="14">
         <v>0.96540000000000004</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15">
+      <c r="A39" s="14">
         <v>3</v>
       </c>
-      <c r="B39" s="15">
-        <v>1</v>
-      </c>
-      <c r="C39" s="15">
-        <v>1</v>
-      </c>
-      <c r="D39" s="15">
+      <c r="B39" s="14">
+        <v>1</v>
+      </c>
+      <c r="C39" s="14">
+        <v>1</v>
+      </c>
+      <c r="D39" s="14">
         <v>0.77159999999999995</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>0.76890000000000003</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="14">
         <v>0</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>0.5</v>
       </c>
-      <c r="H39" s="19">
-        <v>1</v>
-      </c>
-      <c r="I39" s="18">
-        <v>1</v>
-      </c>
-      <c r="J39" s="15">
+      <c r="H39" s="17">
+        <v>1</v>
+      </c>
+      <c r="I39" s="16">
+        <v>1</v>
+      </c>
+      <c r="J39" s="14">
         <v>0.18459999999999999</v>
       </c>
-      <c r="K39" s="15">
-        <v>0.17749999999999999</v>
+      <c r="K39" s="14">
+        <v>0.58099999999999996</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="15">
+      <c r="A40" s="14">
         <v>4</v>
       </c>
-      <c r="B40" s="15">
-        <v>1</v>
-      </c>
-      <c r="C40" s="15">
-        <v>1</v>
-      </c>
-      <c r="D40" s="15">
+      <c r="B40" s="14">
+        <v>1</v>
+      </c>
+      <c r="C40" s="14">
+        <v>1</v>
+      </c>
+      <c r="D40" s="14">
         <v>0.77849999999999997</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>0.77569999999999995</v>
       </c>
-      <c r="F40" s="15">
-        <v>1</v>
-      </c>
-      <c r="G40" s="15">
-        <v>1</v>
-      </c>
-      <c r="H40" s="19">
-        <v>1</v>
-      </c>
-      <c r="I40" s="18">
-        <v>1</v>
-      </c>
-      <c r="J40" s="15">
+      <c r="F40" s="14">
+        <v>1</v>
+      </c>
+      <c r="G40" s="14">
+        <v>1</v>
+      </c>
+      <c r="H40" s="17">
+        <v>1</v>
+      </c>
+      <c r="I40" s="16">
+        <v>1</v>
+      </c>
+      <c r="J40" s="14">
         <v>0.95609999999999995</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="14">
         <v>0.95609999999999995</v>
       </c>
       <c r="R40" s="6"/>
     </row>
     <row r="41" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15">
+      <c r="A41" s="14">
         <v>5</v>
       </c>
-      <c r="B41" s="15">
-        <v>1</v>
-      </c>
-      <c r="C41" s="15">
-        <v>1</v>
-      </c>
-      <c r="D41" s="15">
+      <c r="B41" s="14">
+        <v>1</v>
+      </c>
+      <c r="C41" s="14">
+        <v>1</v>
+      </c>
+      <c r="D41" s="14">
         <v>0.77</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>0.75239999999999996</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="14">
         <v>0.41670000000000001</v>
       </c>
-      <c r="G41" s="15">
-        <v>1</v>
-      </c>
-      <c r="H41" s="19">
-        <v>1</v>
-      </c>
-      <c r="I41" s="18">
-        <v>1</v>
-      </c>
-      <c r="J41" s="15">
+      <c r="G41" s="14">
+        <v>1</v>
+      </c>
+      <c r="H41" s="17">
+        <v>1</v>
+      </c>
+      <c r="I41" s="16">
+        <v>1</v>
+      </c>
+      <c r="J41" s="14">
         <v>0.2011</v>
       </c>
-      <c r="K41" s="15">
+      <c r="K41" s="14">
         <v>0.96279999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
+      <c r="A42" s="14">
         <v>6</v>
       </c>
-      <c r="B42" s="15">
-        <v>1</v>
-      </c>
-      <c r="C42" s="15">
-        <v>1</v>
-      </c>
-      <c r="D42" s="15">
+      <c r="B42" s="14">
+        <v>1</v>
+      </c>
+      <c r="C42" s="14">
+        <v>1</v>
+      </c>
+      <c r="D42" s="14">
         <v>0.70140000000000002</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>0.79339999999999999</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="14">
         <v>0.5</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>0.83330000000000004</v>
       </c>
-      <c r="H42" s="19">
-        <v>1</v>
-      </c>
-      <c r="I42" s="18">
-        <v>1</v>
-      </c>
-      <c r="J42" s="15">
+      <c r="H42" s="17">
+        <v>1</v>
+      </c>
+      <c r="I42" s="16">
+        <v>1</v>
+      </c>
+      <c r="J42" s="14">
         <v>0.48420000000000002</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="14">
         <v>0.57050000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15">
+      <c r="A43" s="14">
         <v>7</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="14">
         <v>0.25</v>
       </c>
-      <c r="C43" s="15">
-        <v>1</v>
-      </c>
-      <c r="D43" s="15">
+      <c r="C43" s="14">
+        <v>1</v>
+      </c>
+      <c r="D43" s="14">
         <v>0.7974</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>0.80100000000000005</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="14">
         <v>0.5</v>
       </c>
-      <c r="G43" s="15">
-        <v>1</v>
-      </c>
-      <c r="H43" s="19">
-        <v>1</v>
-      </c>
-      <c r="I43" s="18">
-        <v>1</v>
-      </c>
-      <c r="J43" s="15">
+      <c r="G43" s="14">
+        <v>1</v>
+      </c>
+      <c r="H43" s="17">
+        <v>1</v>
+      </c>
+      <c r="I43" s="16">
+        <v>1</v>
+      </c>
+      <c r="J43" s="14">
         <v>0.41120000000000001</v>
       </c>
-      <c r="K43" s="15">
+      <c r="K43" s="14">
         <v>0.95789999999999997</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="15">
+      <c r="A44" s="14">
         <v>8</v>
       </c>
-      <c r="B44" s="15">
-        <v>1</v>
-      </c>
-      <c r="C44" s="15">
-        <v>1</v>
-      </c>
-      <c r="D44" s="15">
+      <c r="B44" s="14">
+        <v>1</v>
+      </c>
+      <c r="C44" s="14">
+        <v>1</v>
+      </c>
+      <c r="D44" s="14">
         <v>0.81399999999999995</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>0.81620000000000004</v>
       </c>
-      <c r="F44" s="15">
-        <v>1</v>
-      </c>
-      <c r="G44" s="15">
-        <v>1</v>
-      </c>
-      <c r="H44" s="19">
-        <v>1</v>
-      </c>
-      <c r="I44" s="18">
-        <v>1</v>
-      </c>
-      <c r="J44" s="15">
+      <c r="F44" s="14">
+        <v>1</v>
+      </c>
+      <c r="G44" s="14">
+        <v>1</v>
+      </c>
+      <c r="H44" s="17">
+        <v>1</v>
+      </c>
+      <c r="I44" s="16">
+        <v>1</v>
+      </c>
+      <c r="J44" s="14">
         <v>0.81489999999999996</v>
       </c>
-      <c r="K44" s="15">
+      <c r="K44" s="14">
         <v>0.81489999999999996</v>
       </c>
     </row>
     <row r="45" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15">
+      <c r="A45" s="14">
         <v>9</v>
       </c>
       <c r="B45" s="8">
@@ -5402,10 +6381,10 @@
       <c r="G45" s="8">
         <v>1</v>
       </c>
-      <c r="H45" s="19">
-        <v>1</v>
-      </c>
-      <c r="I45" s="19">
+      <c r="H45" s="17">
+        <v>1</v>
+      </c>
+      <c r="I45" s="17">
         <v>1</v>
       </c>
       <c r="J45" s="8">
@@ -5417,7 +6396,7 @@
     </row>
     <row r="46" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B46" s="8">
         <f>AVERAGE(B36:B45)</f>
@@ -5443,11 +6422,11 @@
         <f>AVERAGE(G36:G45)</f>
         <v>0.9333300000000001</v>
       </c>
-      <c r="H46" s="19">
+      <c r="H46" s="17">
         <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
-      <c r="I46" s="19">
+      <c r="I46" s="17">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -5457,7 +6436,7 @@
       </c>
       <c r="K46" s="8">
         <f t="shared" si="2"/>
-        <v>0.82812999999999981</v>
+        <v>0.86847999999999992</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
@@ -5475,19 +6454,19 @@
       <c r="Q47" s="6"/>
     </row>
     <row r="48" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
+      <c r="A48" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="25"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
@@ -5497,339 +6476,339 @@
       <c r="R48" s="6"/>
     </row>
     <row r="49" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="25"/>
+      <c r="F49" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28" t="s">
+      <c r="G49" s="26"/>
+      <c r="H49" s="27"/>
+      <c r="I49" s="27"/>
+      <c r="J49" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E49" s="28"/>
-      <c r="F49" s="29" t="s">
+      <c r="K49" s="25"/>
+    </row>
+    <row r="50" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="25"/>
+      <c r="B50" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="K50" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="21">
+        <v>0</v>
+      </c>
+      <c r="B51" s="21">
+        <v>1</v>
+      </c>
+      <c r="C51" s="21">
+        <v>1</v>
+      </c>
+      <c r="D51" s="21">
+        <v>0.77769999999999995</v>
+      </c>
+      <c r="E51" s="21">
+        <v>0.77769999999999995</v>
+      </c>
+      <c r="F51" s="21">
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="G51" s="21">
+        <v>1</v>
+      </c>
+      <c r="H51" s="17"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="21">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="K51" s="21">
+        <v>0.96199999999999997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="21">
+        <v>1</v>
+      </c>
+      <c r="B52" s="21">
+        <v>1</v>
+      </c>
+      <c r="C52" s="21">
+        <v>1</v>
+      </c>
+      <c r="D52" s="21">
+        <v>0.77610000000000001</v>
+      </c>
+      <c r="E52" s="21">
+        <v>0.79059999999999997</v>
+      </c>
+      <c r="F52" s="21">
+        <v>1</v>
+      </c>
+      <c r="G52" s="21">
+        <v>1</v>
+      </c>
+      <c r="H52" s="17"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="21">
+        <v>0.95579999999999998</v>
+      </c>
+      <c r="K52" s="21">
+        <v>0.95579999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="21">
+        <v>2</v>
+      </c>
+      <c r="B53" s="21">
+        <v>1</v>
+      </c>
+      <c r="C53" s="21">
+        <v>1</v>
+      </c>
+      <c r="D53" s="21">
+        <v>0.74919999999999998</v>
+      </c>
+      <c r="E53" s="21">
+        <v>0.77710000000000001</v>
+      </c>
+      <c r="F53" s="21">
+        <v>1</v>
+      </c>
+      <c r="G53" s="21">
+        <v>1</v>
+      </c>
+      <c r="H53" s="17"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="21">
+        <v>0.96540000000000004</v>
+      </c>
+      <c r="K53" s="21">
+        <v>0.96540000000000004</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="21">
         <v>3</v>
       </c>
-      <c r="G49" s="29"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="28" t="s">
+      <c r="B54" s="21">
+        <v>0</v>
+      </c>
+      <c r="C54" s="21">
+        <v>1</v>
+      </c>
+      <c r="D54" s="21">
+        <v>0.76949999999999996</v>
+      </c>
+      <c r="E54" s="21">
+        <v>0.78680000000000005</v>
+      </c>
+      <c r="F54" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="G54" s="21">
+        <v>1</v>
+      </c>
+      <c r="H54" s="17"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="21">
+        <v>0.17680000000000001</v>
+      </c>
+      <c r="K54" s="21">
+        <v>0.95599999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="21">
+        <v>4</v>
+      </c>
+      <c r="B55" s="21">
+        <v>1</v>
+      </c>
+      <c r="C55" s="21">
+        <v>1</v>
+      </c>
+      <c r="D55" s="21">
+        <v>0.77569999999999995</v>
+      </c>
+      <c r="E55" s="21">
+        <v>0.77569999999999995</v>
+      </c>
+      <c r="F55" s="21">
+        <v>1</v>
+      </c>
+      <c r="G55" s="21">
+        <v>1</v>
+      </c>
+      <c r="H55" s="17"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="21">
+        <v>0.95609999999999995</v>
+      </c>
+      <c r="K55" s="21">
+        <v>0.95609999999999995</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="21">
+        <v>5</v>
+      </c>
+      <c r="B56" s="21">
+        <v>1</v>
+      </c>
+      <c r="C56" s="21">
+        <v>1</v>
+      </c>
+      <c r="D56" s="21">
+        <v>0.77</v>
+      </c>
+      <c r="E56" s="21">
+        <v>0.77</v>
+      </c>
+      <c r="F56" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="G56" s="21">
+        <v>1</v>
+      </c>
+      <c r="H56" s="17"/>
+      <c r="I56" s="22"/>
+      <c r="J56" s="21">
+        <v>0.2011</v>
+      </c>
+      <c r="K56" s="21">
+        <v>0.96279999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="21">
         <v>6</v>
       </c>
-      <c r="K49" s="28"/>
-    </row>
-    <row r="50" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="28"/>
-      <c r="B50" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="K50" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="L50" s="6"/>
-    </row>
-    <row r="51" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="23">
+      <c r="B57" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C57" s="21">
+        <v>1</v>
+      </c>
+      <c r="D57" s="21">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="E57" s="21">
+        <v>0.79700000000000004</v>
+      </c>
+      <c r="F57" s="21">
+        <v>1</v>
+      </c>
+      <c r="G57" s="21">
+        <v>1</v>
+      </c>
+      <c r="H57" s="17"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="21">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="K57" s="21">
+        <v>0.58599999999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="21">
+        <v>7</v>
+      </c>
+      <c r="B58" s="21">
         <v>0</v>
       </c>
-      <c r="B51" s="23">
-        <v>1</v>
-      </c>
-      <c r="C51" s="23">
-        <v>1</v>
-      </c>
-      <c r="D51" s="23">
-        <v>0.77769999999999995</v>
-      </c>
-      <c r="E51" s="23">
-        <v>0.77769999999999995</v>
-      </c>
-      <c r="F51" s="23">
-        <v>0.41670000000000001</v>
-      </c>
-      <c r="G51" s="23">
-        <v>1</v>
-      </c>
-      <c r="H51" s="19"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="23">
-        <v>0.96199999999999997</v>
-      </c>
-      <c r="K51" s="23">
-        <v>0.96199999999999997</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="23">
-        <v>1</v>
-      </c>
-      <c r="B52" s="23">
-        <v>1</v>
-      </c>
-      <c r="C52" s="23">
-        <v>1</v>
-      </c>
-      <c r="D52" s="23">
-        <v>0.77610000000000001</v>
-      </c>
-      <c r="E52" s="23">
-        <v>0.79059999999999997</v>
-      </c>
-      <c r="F52" s="23">
-        <v>1</v>
-      </c>
-      <c r="G52" s="23">
-        <v>1</v>
-      </c>
-      <c r="H52" s="19"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="23">
-        <v>0.95579999999999998</v>
-      </c>
-      <c r="K52" s="23">
-        <v>0.95579999999999998</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="23">
-        <v>2</v>
-      </c>
-      <c r="B53" s="23">
-        <v>1</v>
-      </c>
-      <c r="C53" s="23">
-        <v>1</v>
-      </c>
-      <c r="D53" s="23">
-        <v>0.74919999999999998</v>
-      </c>
-      <c r="E53" s="23">
-        <v>0.77710000000000001</v>
-      </c>
-      <c r="F53" s="23">
-        <v>1</v>
-      </c>
-      <c r="G53" s="23">
-        <v>1</v>
-      </c>
-      <c r="H53" s="19"/>
-      <c r="I53" s="24"/>
-      <c r="J53" s="23">
-        <v>0.96540000000000004</v>
-      </c>
-      <c r="K53" s="23">
-        <v>0.96540000000000004</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="23">
-        <v>3</v>
-      </c>
-      <c r="B54" s="23">
-        <v>0</v>
-      </c>
-      <c r="C54" s="23">
-        <v>1</v>
-      </c>
-      <c r="D54" s="23">
-        <v>0.76949999999999996</v>
-      </c>
-      <c r="E54" s="23">
-        <v>0.78680000000000005</v>
-      </c>
-      <c r="F54" s="23">
+      <c r="C58" s="21">
+        <v>1</v>
+      </c>
+      <c r="D58" s="21">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="E58" s="21">
+        <v>0.79579999999999995</v>
+      </c>
+      <c r="F58" s="21">
         <v>0.5</v>
       </c>
-      <c r="G54" s="23">
-        <v>1</v>
-      </c>
-      <c r="H54" s="19"/>
-      <c r="I54" s="24"/>
-      <c r="J54" s="23">
-        <v>0.17680000000000001</v>
-      </c>
-      <c r="K54" s="23">
-        <v>0.95599999999999996</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="23">
-        <v>4</v>
-      </c>
-      <c r="B55" s="23">
-        <v>1</v>
-      </c>
-      <c r="C55" s="23">
-        <v>1</v>
-      </c>
-      <c r="D55" s="23">
-        <v>0.77569999999999995</v>
-      </c>
-      <c r="E55" s="23">
-        <v>0.77569999999999995</v>
-      </c>
-      <c r="F55" s="23">
-        <v>1</v>
-      </c>
-      <c r="G55" s="23">
-        <v>1</v>
-      </c>
-      <c r="H55" s="19"/>
-      <c r="I55" s="24"/>
-      <c r="J55" s="23">
-        <v>0.95609999999999995</v>
-      </c>
-      <c r="K55" s="23">
-        <v>0.95609999999999995</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="23">
-        <v>5</v>
-      </c>
-      <c r="B56" s="23">
-        <v>1</v>
-      </c>
-      <c r="C56" s="23">
-        <v>1</v>
-      </c>
-      <c r="D56" s="23">
-        <v>0.77</v>
-      </c>
-      <c r="E56" s="23">
-        <v>0.77</v>
-      </c>
-      <c r="F56" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G56" s="23">
-        <v>1</v>
-      </c>
-      <c r="H56" s="19"/>
-      <c r="I56" s="24"/>
-      <c r="J56" s="23">
-        <v>0.2011</v>
-      </c>
-      <c r="K56" s="23">
-        <v>0.2011</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="23">
-        <v>6</v>
-      </c>
-      <c r="B57" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="C57" s="23">
-        <v>1</v>
-      </c>
-      <c r="D57" s="23">
-        <v>0.79700000000000004</v>
-      </c>
-      <c r="E57" s="23">
-        <v>0.79700000000000004</v>
-      </c>
-      <c r="F57" s="23">
-        <v>1</v>
-      </c>
-      <c r="G57" s="23">
-        <v>1</v>
-      </c>
-      <c r="H57" s="19"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="23">
-        <v>0.58599999999999997</v>
-      </c>
-      <c r="K57" s="23">
-        <v>0.58599999999999997</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="23">
-        <v>7</v>
-      </c>
-      <c r="B58" s="23">
-        <v>0</v>
-      </c>
-      <c r="C58" s="23">
-        <v>1</v>
-      </c>
-      <c r="D58" s="23">
-        <v>0.80500000000000005</v>
-      </c>
-      <c r="E58" s="23">
-        <v>0.79579999999999995</v>
-      </c>
-      <c r="F58" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G58" s="23">
-        <v>1</v>
-      </c>
-      <c r="H58" s="19"/>
-      <c r="I58" s="24"/>
-      <c r="J58" s="23">
+      <c r="G58" s="21">
+        <v>1</v>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="21">
         <v>0.70089999999999997</v>
       </c>
-      <c r="K58" s="23">
+      <c r="K58" s="21">
         <v>0.95789999999999997</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="23">
+      <c r="A59" s="21">
         <v>8</v>
       </c>
-      <c r="B59" s="23">
-        <v>1</v>
-      </c>
-      <c r="C59" s="23">
-        <v>1</v>
-      </c>
-      <c r="D59" s="23">
+      <c r="B59" s="21">
+        <v>1</v>
+      </c>
+      <c r="C59" s="21">
+        <v>1</v>
+      </c>
+      <c r="D59" s="21">
         <v>0.81620000000000004</v>
       </c>
-      <c r="E59" s="23">
+      <c r="E59" s="21">
         <v>0.81620000000000004</v>
       </c>
-      <c r="F59" s="23">
-        <v>1</v>
-      </c>
-      <c r="G59" s="23">
-        <v>1</v>
-      </c>
-      <c r="H59" s="19"/>
-      <c r="I59" s="24"/>
-      <c r="J59" s="23">
+      <c r="F59" s="21">
+        <v>1</v>
+      </c>
+      <c r="G59" s="21">
+        <v>1</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="21">
         <v>0.81489999999999996</v>
       </c>
-      <c r="K59" s="23">
+      <c r="K59" s="21">
         <v>0.81489999999999996</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="23">
+      <c r="A60" s="21">
         <v>9</v>
       </c>
       <c r="B60" s="8">
@@ -5850,8 +6829,8 @@
       <c r="G60" s="8">
         <v>1</v>
       </c>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
       <c r="J60" s="8">
         <v>0.18049999999999999</v>
       </c>
@@ -5861,7 +6840,7 @@
     </row>
     <row r="61" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" s="8">
         <f>AVERAGE(B51:B60)</f>
@@ -5887,15 +6866,15 @@
         <f>AVERAGE(G51:G60)</f>
         <v>1</v>
       </c>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
       <c r="J61" s="8">
         <f t="shared" si="3"/>
         <v>0.64995000000000003</v>
       </c>
       <c r="K61" s="8">
         <f t="shared" si="3"/>
-        <v>0.83135999999999988</v>
+        <v>0.90752999999999984</v>
       </c>
     </row>
   </sheetData>
@@ -5936,23 +6915,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA574D9-6098-4E7A-94F4-A2DD9F4FC518}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="16.77734375" defaultRowHeight="25.05" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.77734375" style="14"/>
-    <col min="3" max="3" width="24" style="14" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="25.21875" style="14" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" style="14" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" style="27" customWidth="1"/>
-    <col min="9" max="9" width="24.88671875" style="14" customWidth="1"/>
-    <col min="10" max="16384" width="16.77734375" style="14"/>
+    <col min="1" max="2" width="16.77734375" style="8"/>
+    <col min="3" max="3" width="24" style="8" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="25.21875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" style="8" customWidth="1"/>
+    <col min="7" max="8" width="21.44140625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="24.88671875" style="8" customWidth="1"/>
+    <col min="10" max="11" width="16.77734375" style="8"/>
+    <col min="12" max="12" width="23" style="8" customWidth="1"/>
+    <col min="13" max="13" width="25" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="16.77734375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -5961,251 +6942,331 @@
       <c r="F1" s="28"/>
       <c r="G1" s="28"/>
     </row>
-    <row r="2" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J3" s="8">
+        <v>24</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J4" s="8">
+        <v>24</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="J5" s="8">
+        <v>24</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="14" t="s">
+      <c r="C6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" s="8">
+        <v>24</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="8">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="8">
+        <v>25</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
-        <v>1</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="J8" s="8">
+        <v>25</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="8">
+        <v>25</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="J3" s="14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
-        <v>2</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
-        <v>3</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="J5" s="14">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="27" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
-        <v>4</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
-        <v>5</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="J7" s="14">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="15" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27">
+    </row>
+    <row r="18" spans="1:1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
         <v>6</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="H8" s="27"/>
-      <c r="I8" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J8" s="15">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
+    </row>
+    <row r="19" spans="1:1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
         <v>7</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="14">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
+    </row>
+    <row r="20" spans="1:1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
         <v>8</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
